--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/Zwischenstände/CAES2024_Datenbank/before_conversion_caes2014_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/Zwischenstände/CAES2024_Datenbank/before_conversion_caes2014_mapped_readable.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="REFLECT Mapped" sheetId="1" r:id="rId1"/>
+    <sheet name="SHEET1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/Zwischenstände/CAES2024_Datenbank/before_conversion_caes2014_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/Zwischenstände/CAES2024_Datenbank/before_conversion_caes2014_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="83">
   <si>
     <t>location</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>HS_in_mmol/L</t>
+  </si>
+  <si>
+    <t>Database_number</t>
   </si>
   <si>
     <t>Jefferson</t>
@@ -623,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC43"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -652,9 +655,10 @@
     <col min="27" max="27" width="15.7109375" customWidth="1"/>
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
+    <col min="30" max="30" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -742,13 +746,16 @@
       <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2">
         <v>43.64283</v>
@@ -786,13 +793,16 @@
       <c r="Z2">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AD2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3">
         <v>44.14558</v>
@@ -830,13 +840,16 @@
       <c r="Z3">
         <v>4.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:29">
+      <c r="AD3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4">
         <v>44.14166</v>
@@ -874,13 +887,16 @@
       <c r="Z4">
         <v>4.7</v>
       </c>
-    </row>
-    <row r="5" spans="1:29">
+      <c r="AD4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5">
         <v>43.79211</v>
@@ -918,13 +934,16 @@
       <c r="Z5">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:29">
+      <c r="AD5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6">
         <v>44.09325</v>
@@ -965,13 +984,16 @@
       <c r="Z6">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="7" spans="1:29">
+      <c r="AD6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7">
         <v>43.33278</v>
@@ -1009,13 +1031,16 @@
       <c r="Z7">
         <v>1.6</v>
       </c>
-    </row>
-    <row r="8" spans="1:29">
+      <c r="AD7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8">
         <v>43.60234</v>
@@ -1056,13 +1081,16 @@
       <c r="Z8">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="9" spans="1:29">
+      <c r="AD8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C9">
         <v>42.6994</v>
@@ -1103,13 +1131,16 @@
       <c r="Z9">
         <v>12.2</v>
       </c>
-    </row>
-    <row r="10" spans="1:29">
+      <c r="AD9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10">
         <v>42.64497</v>
@@ -1150,13 +1181,16 @@
       <c r="Z10">
         <v>2.2</v>
       </c>
-    </row>
-    <row r="11" spans="1:29">
+      <c r="AD10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11">
         <v>42.64432</v>
@@ -1197,13 +1231,16 @@
       <c r="Z11">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:29">
+      <c r="AD11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12">
         <v>42.69457</v>
@@ -1241,13 +1278,16 @@
       <c r="Z12">
         <v>22.4</v>
       </c>
-    </row>
-    <row r="13" spans="1:29">
+      <c r="AD12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13">
         <v>42.54479</v>
@@ -1288,13 +1328,16 @@
       <c r="Z13">
         <v>2.4</v>
       </c>
-    </row>
-    <row r="14" spans="1:29">
+      <c r="AD13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14">
         <v>42.54348</v>
@@ -1332,13 +1375,16 @@
       <c r="Z14">
         <v>2.4</v>
       </c>
-    </row>
-    <row r="15" spans="1:29">
+      <c r="AD14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15">
         <v>42.58318</v>
@@ -1379,13 +1425,16 @@
       <c r="Z15">
         <v>9.6</v>
       </c>
-    </row>
-    <row r="16" spans="1:29">
+      <c r="AD15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C16">
         <v>43.44244</v>
@@ -1423,13 +1472,16 @@
       <c r="Z16">
         <v>0.3773</v>
       </c>
-    </row>
-    <row r="17" spans="1:26">
+      <c r="AD16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C17">
         <v>43.43774</v>
@@ -1467,13 +1519,16 @@
       <c r="Z17">
         <v>0.2672</v>
       </c>
-    </row>
-    <row r="18" spans="1:26">
+      <c r="AD17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C18">
         <v>43.43142</v>
@@ -1511,13 +1566,16 @@
       <c r="Z18">
         <v>0.2264</v>
       </c>
-    </row>
-    <row r="19" spans="1:26">
+      <c r="AD18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C19">
         <v>43.43121</v>
@@ -1555,13 +1613,16 @@
       <c r="Z19">
         <v>0.2552</v>
       </c>
-    </row>
-    <row r="20" spans="1:26">
+      <c r="AD19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>43.64283</v>
@@ -1599,13 +1660,16 @@
       <c r="Z20">
         <v>-99999</v>
       </c>
-    </row>
-    <row r="21" spans="1:26">
+      <c r="AD20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C21">
         <v>42.10207</v>
@@ -1643,13 +1707,16 @@
       <c r="Z21">
         <v>2.198</v>
       </c>
-    </row>
-    <row r="22" spans="1:26">
+      <c r="AD21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C22">
         <v>42.11042</v>
@@ -1687,13 +1754,16 @@
       <c r="Z22">
         <v>4.638</v>
       </c>
-    </row>
-    <row r="23" spans="1:26">
+      <c r="AD22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23">
         <v>42.08359</v>
@@ -1731,13 +1801,16 @@
       <c r="Z23">
         <v>6.045</v>
       </c>
-    </row>
-    <row r="24" spans="1:26">
+      <c r="AD23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C24">
         <v>42.09787</v>
@@ -1775,13 +1848,16 @@
       <c r="Z24">
         <v>7.1511</v>
       </c>
-    </row>
-    <row r="25" spans="1:26">
+      <c r="AD24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C25">
         <v>42.72589</v>
@@ -1819,13 +1895,16 @@
       <c r="Z25">
         <v>0.5021</v>
       </c>
-    </row>
-    <row r="26" spans="1:26">
+      <c r="AD25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26">
         <v>42.23667</v>
@@ -1863,13 +1942,16 @@
       <c r="Z26">
         <v>6.6983</v>
       </c>
-    </row>
-    <row r="27" spans="1:26">
+      <c r="AD26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27">
         <v>42.107989</v>
@@ -1907,13 +1989,16 @@
       <c r="Z27">
         <v>7.0441</v>
       </c>
-    </row>
-    <row r="28" spans="1:26">
+      <c r="AD27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28">
         <v>42.10776</v>
@@ -1951,13 +2036,16 @@
       <c r="Z28">
         <v>5.8205</v>
       </c>
-    </row>
-    <row r="29" spans="1:26">
+      <c r="AD28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29">
         <v>42.09656</v>
@@ -1995,13 +2083,16 @@
       <c r="Z29">
         <v>6.0714</v>
       </c>
-    </row>
-    <row r="30" spans="1:26">
+      <c r="AD29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C30">
         <v>43.36414</v>
@@ -2039,13 +2130,16 @@
       <c r="Z30">
         <v>1.8508</v>
       </c>
-    </row>
-    <row r="31" spans="1:26">
+      <c r="AD30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31">
         <v>43.42818</v>
@@ -2083,13 +2177,16 @@
       <c r="Z31">
         <v>10.5715</v>
       </c>
-    </row>
-    <row r="32" spans="1:26">
+      <c r="AD31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32">
         <v>43.42341</v>
@@ -2127,13 +2224,16 @@
       <c r="Z32">
         <v>15.1266</v>
       </c>
-    </row>
-    <row r="33" spans="1:26">
+      <c r="AD32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33">
         <v>43.42322</v>
@@ -2171,13 +2271,16 @@
       <c r="Z33">
         <v>15.1678</v>
       </c>
-    </row>
-    <row r="34" spans="1:26">
+      <c r="AD33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C34">
         <v>43.29241</v>
@@ -2215,13 +2318,16 @@
       <c r="Z34">
         <v>7.0787</v>
       </c>
-    </row>
-    <row r="35" spans="1:26">
+      <c r="AD34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35">
         <v>43.3829</v>
@@ -2259,13 +2365,16 @@
       <c r="Z35">
         <v>3.3517</v>
       </c>
-    </row>
-    <row r="36" spans="1:26">
+      <c r="AD35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C36">
         <v>43.32777</v>
@@ -2303,13 +2412,16 @@
       <c r="Z36">
         <v>9.9489</v>
       </c>
-    </row>
-    <row r="37" spans="1:26">
+      <c r="AD36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C37">
         <v>43.12966</v>
@@ -2347,13 +2459,16 @@
       <c r="Z37">
         <v>6.9537</v>
       </c>
-    </row>
-    <row r="38" spans="1:26">
+      <c r="AD37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C38">
         <v>42.17334</v>
@@ -2391,13 +2506,16 @@
       <c r="Z38">
         <v>7.6095</v>
       </c>
-    </row>
-    <row r="39" spans="1:26">
+      <c r="AD38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C39">
         <v>42.08533</v>
@@ -2435,13 +2553,16 @@
       <c r="Z39">
         <v>2.4245</v>
       </c>
-    </row>
-    <row r="40" spans="1:26">
+      <c r="AD39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C40">
         <v>42.47663</v>
@@ -2479,13 +2600,16 @@
       <c r="Z40">
         <v>13.1831</v>
       </c>
-    </row>
-    <row r="41" spans="1:26">
+      <c r="AD40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C41">
         <v>42.70399</v>
@@ -2523,13 +2647,16 @@
       <c r="Z41">
         <v>24.2219</v>
       </c>
-    </row>
-    <row r="42" spans="1:26">
+      <c r="AD41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C42">
         <v>42.68841</v>
@@ -2567,13 +2694,16 @@
       <c r="Z42">
         <v>11.3885</v>
       </c>
-    </row>
-    <row r="43" spans="1:26">
+      <c r="AD42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C43">
         <v>42.68841</v>
@@ -2610,6 +2740,9 @@
       </c>
       <c r="Z43">
         <v>11.3566</v>
+      </c>
+      <c r="AD43">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/Zwischenstände/CAES2024_Datenbank/before_conversion_caes2014_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/Zwischenstände/CAES2024_Datenbank/before_conversion_caes2014_mapped_readable.xlsx
@@ -638,7 +638,7 @@
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="18.7109375" customWidth="1"/>
     <col min="9" max="9" width="38.7109375" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" customWidth="1"/>
     <col min="11" max="11" width="23.7109375" customWidth="1"/>
     <col min="12" max="12" width="34.7109375" customWidth="1"/>
     <col min="13" max="14" width="14.7109375" customWidth="1"/>
@@ -648,7 +648,7 @@
     <col min="19" max="19" width="16.7109375" customWidth="1"/>
     <col min="20" max="20" width="15.7109375" customWidth="1"/>
     <col min="21" max="21" width="13.7109375" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" customWidth="1"/>
+    <col min="22" max="22" width="17.7109375" customWidth="1"/>
     <col min="23" max="23" width="15.7109375" customWidth="1"/>
     <col min="24" max="25" width="14.7109375" customWidth="1"/>
     <col min="26" max="26" width="13.7109375" customWidth="1"/>
@@ -766,6 +766,9 @@
       <c r="H2">
         <v>48.2</v>
       </c>
+      <c r="J2">
+        <v>6.32</v>
+      </c>
       <c r="N2">
         <v>1540</v>
       </c>
@@ -789,6 +792,9 @@
       </c>
       <c r="U2">
         <v>206</v>
+      </c>
+      <c r="V2">
+        <v>5.466</v>
       </c>
       <c r="Z2">
         <v>4</v>
@@ -813,6 +819,9 @@
       <c r="H3">
         <v>56.1</v>
       </c>
+      <c r="J3">
+        <v>7.17</v>
+      </c>
       <c r="N3">
         <v>25</v>
       </c>
@@ -836,6 +845,9 @@
       </c>
       <c r="U3">
         <v>13.2</v>
+      </c>
+      <c r="V3">
+        <v>0.597</v>
       </c>
       <c r="Z3">
         <v>4.6</v>
@@ -860,6 +872,9 @@
       <c r="H4">
         <v>52.3</v>
       </c>
+      <c r="J4">
+        <v>7.21</v>
+      </c>
       <c r="N4">
         <v>28</v>
       </c>
@@ -883,6 +898,9 @@
       </c>
       <c r="U4">
         <v>13.5</v>
+      </c>
+      <c r="V4">
+        <v>0.611</v>
       </c>
       <c r="Z4">
         <v>4.7</v>
@@ -907,6 +925,9 @@
       <c r="H5">
         <v>44</v>
       </c>
+      <c r="J5">
+        <v>7.2</v>
+      </c>
       <c r="N5">
         <v>5</v>
       </c>
@@ -930,6 +951,9 @@
       </c>
       <c r="U5">
         <v>4.5</v>
+      </c>
+      <c r="V5">
+        <v>1.172</v>
       </c>
       <c r="Z5">
         <v>1.5</v>
@@ -957,6 +981,9 @@
       <c r="H6">
         <v>31.4</v>
       </c>
+      <c r="J6">
+        <v>8.73</v>
+      </c>
       <c r="N6">
         <v>33</v>
       </c>
@@ -980,6 +1007,9 @@
       </c>
       <c r="U6">
         <v>0.9</v>
+      </c>
+      <c r="V6">
+        <v>0.005</v>
       </c>
       <c r="Z6">
         <v>2.1</v>
@@ -1004,6 +1034,9 @@
       <c r="H7">
         <v>50.5</v>
       </c>
+      <c r="J7">
+        <v>7.03</v>
+      </c>
       <c r="N7">
         <v>62</v>
       </c>
@@ -1027,6 +1060,9 @@
       </c>
       <c r="U7">
         <v>22.5</v>
+      </c>
+      <c r="V7">
+        <v>0.9320000000000001</v>
       </c>
       <c r="Z7">
         <v>1.6</v>
@@ -1054,6 +1090,9 @@
       <c r="H8">
         <v>36.3</v>
       </c>
+      <c r="J8">
+        <v>7.09</v>
+      </c>
       <c r="N8">
         <v>34</v>
       </c>
@@ -1077,6 +1116,9 @@
       </c>
       <c r="U8">
         <v>9.4</v>
+      </c>
+      <c r="V8">
+        <v>0.723</v>
       </c>
       <c r="Z8">
         <v>0.7</v>
@@ -1104,6 +1146,9 @@
       <c r="H9">
         <v>24.7</v>
       </c>
+      <c r="J9">
+        <v>9.470000000000001</v>
+      </c>
       <c r="N9">
         <v>113</v>
       </c>
@@ -1127,6 +1172,9 @@
       </c>
       <c r="U9">
         <v>4.2</v>
+      </c>
+      <c r="V9">
+        <v>0.022</v>
       </c>
       <c r="Z9">
         <v>12.2</v>
@@ -1154,6 +1202,9 @@
       <c r="H10">
         <v>34.5</v>
       </c>
+      <c r="J10">
+        <v>7.98</v>
+      </c>
       <c r="N10">
         <v>58</v>
       </c>
@@ -1177,6 +1228,9 @@
       </c>
       <c r="U10">
         <v>7.7</v>
+      </c>
+      <c r="V10">
+        <v>0.156</v>
       </c>
       <c r="Z10">
         <v>2.2</v>
@@ -1204,6 +1258,9 @@
       <c r="H11">
         <v>34.4</v>
       </c>
+      <c r="J11">
+        <v>7.96</v>
+      </c>
       <c r="N11">
         <v>56</v>
       </c>
@@ -1227,6 +1284,9 @@
       </c>
       <c r="U11">
         <v>8</v>
+      </c>
+      <c r="V11">
+        <v>0.177</v>
       </c>
       <c r="Z11">
         <v>2.5</v>
@@ -1251,6 +1311,9 @@
       <c r="H12">
         <v>58.4</v>
       </c>
+      <c r="J12">
+        <v>9.529999999999999</v>
+      </c>
       <c r="N12">
         <v>128</v>
       </c>
@@ -1274,6 +1337,9 @@
       </c>
       <c r="U12">
         <v>1.9</v>
+      </c>
+      <c r="V12">
+        <v>0.001</v>
       </c>
       <c r="Z12">
         <v>22.4</v>
@@ -1301,6 +1367,9 @@
       <c r="H13">
         <v>37.5</v>
       </c>
+      <c r="J13">
+        <v>8.59</v>
+      </c>
       <c r="N13">
         <v>149</v>
       </c>
@@ -1324,6 +1393,9 @@
       </c>
       <c r="U13">
         <v>1.4</v>
+      </c>
+      <c r="V13">
+        <v>0.063</v>
       </c>
       <c r="Z13">
         <v>2.4</v>
@@ -1348,6 +1420,9 @@
       <c r="H14">
         <v>36.2</v>
       </c>
+      <c r="J14">
+        <v>8.65</v>
+      </c>
       <c r="N14">
         <v>147</v>
       </c>
@@ -1371,6 +1446,9 @@
       </c>
       <c r="U14">
         <v>1.9</v>
+      </c>
+      <c r="V14">
+        <v>0.065</v>
       </c>
       <c r="Z14">
         <v>2.4</v>
@@ -1398,6 +1476,9 @@
       <c r="H15">
         <v>38.1</v>
       </c>
+      <c r="J15">
+        <v>8.789999999999999</v>
+      </c>
       <c r="N15">
         <v>95</v>
       </c>
@@ -1421,6 +1502,9 @@
       </c>
       <c r="U15">
         <v>3.3</v>
+      </c>
+      <c r="V15">
+        <v>0.019</v>
       </c>
       <c r="Z15">
         <v>9.6</v>
@@ -1445,6 +1529,9 @@
       <c r="H16">
         <v>20.9</v>
       </c>
+      <c r="J16">
+        <v>6.7</v>
+      </c>
       <c r="N16">
         <v>96.6627</v>
       </c>
@@ -1468,6 +1555,9 @@
       </c>
       <c r="U16">
         <v>15.9691</v>
+      </c>
+      <c r="V16">
+        <v>0.3108148129</v>
       </c>
       <c r="Z16">
         <v>0.3773</v>
@@ -1492,6 +1582,9 @@
       <c r="H17">
         <v>27.7</v>
       </c>
+      <c r="J17">
+        <v>6.94</v>
+      </c>
       <c r="N17">
         <v>89.7474</v>
       </c>
@@ -1515,6 +1608,9 @@
       </c>
       <c r="U17">
         <v>15.7708</v>
+      </c>
+      <c r="V17">
+        <v>0.2431327363</v>
       </c>
       <c r="Z17">
         <v>0.2672</v>
@@ -1539,6 +1635,9 @@
       <c r="H18">
         <v>26.8</v>
       </c>
+      <c r="J18">
+        <v>6.64</v>
+      </c>
       <c r="N18">
         <v>124.4274</v>
       </c>
@@ -1562,6 +1661,9 @@
       </c>
       <c r="U18">
         <v>17.2911</v>
+      </c>
+      <c r="V18">
+        <v>0.4046644484</v>
       </c>
       <c r="Z18">
         <v>0.2264</v>
@@ -1586,6 +1688,9 @@
       <c r="H19">
         <v>25.1</v>
       </c>
+      <c r="J19">
+        <v>6.77</v>
+      </c>
       <c r="N19">
         <v>122.2332</v>
       </c>
@@ -1609,6 +1714,9 @@
       </c>
       <c r="U19">
         <v>16.7395</v>
+      </c>
+      <c r="V19">
+        <v>0.4296428051</v>
       </c>
       <c r="Z19">
         <v>0.2552</v>
@@ -1633,6 +1741,9 @@
       <c r="H20">
         <v>48.6</v>
       </c>
+      <c r="J20">
+        <v>6.31</v>
+      </c>
       <c r="N20">
         <v>-99999</v>
       </c>
@@ -1655,6 +1766,9 @@
         <v>-99999</v>
       </c>
       <c r="U20">
+        <v>-99999</v>
+      </c>
+      <c r="V20">
         <v>-99999</v>
       </c>
       <c r="Z20">
@@ -1680,6 +1794,9 @@
       <c r="H21">
         <v>59.7</v>
       </c>
+      <c r="J21">
+        <v>7.05</v>
+      </c>
       <c r="N21">
         <v>567.7173</v>
       </c>
@@ -1703,6 +1820,9 @@
       </c>
       <c r="U21">
         <v>39.8943</v>
+      </c>
+      <c r="V21">
+        <v>1.527271647</v>
       </c>
       <c r="Z21">
         <v>2.198</v>
@@ -1727,6 +1847,9 @@
       <c r="H22">
         <v>47.9</v>
       </c>
+      <c r="J22">
+        <v>6.92</v>
+      </c>
       <c r="N22">
         <v>418.222898</v>
       </c>
@@ -1750,6 +1873,9 @@
       </c>
       <c r="U22">
         <v>37.888</v>
+      </c>
+      <c r="V22">
+        <v>1.224323209</v>
       </c>
       <c r="Z22">
         <v>4.638</v>
@@ -1774,6 +1900,9 @@
       <c r="H23">
         <v>48</v>
       </c>
+      <c r="J23">
+        <v>6.3</v>
+      </c>
       <c r="N23">
         <v>1258.190865</v>
       </c>
@@ -1797,6 +1926,9 @@
       </c>
       <c r="U23">
         <v>150.2831</v>
+      </c>
+      <c r="V23">
+        <v>4.931090277</v>
       </c>
       <c r="Z23">
         <v>6.045</v>
@@ -1821,6 +1953,9 @@
       <c r="H24">
         <v>48.3</v>
       </c>
+      <c r="J24">
+        <v>7.07</v>
+      </c>
       <c r="N24">
         <v>542.5483931</v>
       </c>
@@ -1844,6 +1979,9 @@
       </c>
       <c r="U24">
         <v>38.821</v>
+      </c>
+      <c r="V24">
+        <v>1.413091881</v>
       </c>
       <c r="Z24">
         <v>7.1511</v>
@@ -1868,6 +2006,9 @@
       <c r="H25">
         <v>32.7</v>
       </c>
+      <c r="J25">
+        <v>7.23</v>
+      </c>
       <c r="N25">
         <v>126.0312937</v>
       </c>
@@ -1891,6 +2032,9 @@
       </c>
       <c r="U25">
         <v>11.4757</v>
+      </c>
+      <c r="V25">
+        <v>2.11516539</v>
       </c>
       <c r="Z25">
         <v>0.5021</v>
@@ -1915,6 +2059,9 @@
       <c r="H26">
         <v>54.7</v>
       </c>
+      <c r="J26">
+        <v>9.210000000000001</v>
+      </c>
       <c r="N26">
         <v>164.0064823</v>
       </c>
@@ -1938,6 +2085,9 @@
       </c>
       <c r="U26">
         <v>2.4873</v>
+      </c>
+      <c r="V26">
+        <v>0.01581816946</v>
       </c>
       <c r="Z26">
         <v>6.6983</v>
@@ -1962,6 +2112,9 @@
       <c r="H27">
         <v>44.7</v>
       </c>
+      <c r="J27">
+        <v>8.119999999999999</v>
+      </c>
       <c r="N27">
         <v>621.4665732</v>
       </c>
@@ -1985,6 +2138,9 @@
       </c>
       <c r="U27">
         <v>24.8465</v>
+      </c>
+      <c r="V27">
+        <v>1.612173538</v>
       </c>
       <c r="Z27">
         <v>7.0441</v>
@@ -2009,6 +2165,9 @@
       <c r="H28">
         <v>40.9</v>
       </c>
+      <c r="J28">
+        <v>7.72</v>
+      </c>
       <c r="N28">
         <v>598.2669241999999</v>
       </c>
@@ -2032,6 +2191,9 @@
       </c>
       <c r="U28">
         <v>22.6093</v>
+      </c>
+      <c r="V28">
+        <v>1.542824534</v>
       </c>
       <c r="Z28">
         <v>5.8205</v>
@@ -2056,6 +2218,9 @@
       <c r="H29">
         <v>26</v>
       </c>
+      <c r="J29">
+        <v>8.27</v>
+      </c>
       <c r="N29">
         <v>1186.916736</v>
       </c>
@@ -2079,6 +2244,9 @@
       </c>
       <c r="U29">
         <v>35.8802</v>
+      </c>
+      <c r="V29">
+        <v>3.116968339</v>
       </c>
       <c r="Z29">
         <v>6.0714</v>
@@ -2103,6 +2271,9 @@
       <c r="H30">
         <v>38.1</v>
       </c>
+      <c r="J30">
+        <v>7.25</v>
+      </c>
       <c r="N30">
         <v>42.95212893</v>
       </c>
@@ -2126,6 +2297,9 @@
       </c>
       <c r="U30">
         <v>8.454800000000001</v>
+      </c>
+      <c r="V30">
+        <v>0.4494090967</v>
       </c>
       <c r="Z30">
         <v>1.8508</v>
@@ -2150,6 +2324,9 @@
       <c r="H31">
         <v>39.1</v>
       </c>
+      <c r="J31">
+        <v>8.609999999999999</v>
+      </c>
       <c r="N31">
         <v>333.0150388</v>
       </c>
@@ -2173,6 +2350,9 @@
       </c>
       <c r="U31">
         <v>20.9311</v>
+      </c>
+      <c r="V31">
+        <v>0.6458739911</v>
       </c>
       <c r="Z31">
         <v>10.5715</v>
@@ -2197,6 +2377,9 @@
       <c r="H32">
         <v>50</v>
       </c>
+      <c r="J32">
+        <v>9.119999999999999</v>
+      </c>
       <c r="N32">
         <v>90.17863795</v>
       </c>
@@ -2220,6 +2403,9 @@
       </c>
       <c r="U32">
         <v>1.6624</v>
+      </c>
+      <c r="V32">
+        <v>0.1094294343</v>
       </c>
       <c r="Z32">
         <v>15.1266</v>
@@ -2244,6 +2430,9 @@
       <c r="H33">
         <v>55.5</v>
       </c>
+      <c r="J33">
+        <v>9.050000000000001</v>
+      </c>
       <c r="N33">
         <v>91.23479441000001</v>
       </c>
@@ -2267,6 +2456,9 @@
       </c>
       <c r="U33">
         <v>1.5699</v>
+      </c>
+      <c r="V33">
+        <v>0.1117556614</v>
       </c>
       <c r="Z33">
         <v>15.1678</v>
@@ -2291,6 +2483,9 @@
       <c r="H34">
         <v>38</v>
       </c>
+      <c r="J34">
+        <v>8.029999999999999</v>
+      </c>
       <c r="N34">
         <v>156.2478286</v>
       </c>
@@ -2314,6 +2509,9 @@
       </c>
       <c r="U34">
         <v>2.9663</v>
+      </c>
+      <c r="V34">
+        <v>0.3564171346</v>
       </c>
       <c r="Z34">
         <v>7.0787</v>
@@ -2338,6 +2536,9 @@
       <c r="H35">
         <v>67.5</v>
       </c>
+      <c r="J35">
+        <v>9.41</v>
+      </c>
       <c r="N35">
         <v>56.01399062</v>
       </c>
@@ -2361,6 +2562,9 @@
       </c>
       <c r="U35">
         <v>0.8773</v>
+      </c>
+      <c r="V35">
+        <v>0.04459230444</v>
       </c>
       <c r="Z35">
         <v>3.3517</v>
@@ -2385,6 +2589,9 @@
       <c r="H36">
         <v>75</v>
       </c>
+      <c r="J36">
+        <v>6.79</v>
+      </c>
       <c r="N36">
         <v>310.5368593</v>
       </c>
@@ -2408,6 +2615,9 @@
       </c>
       <c r="U36">
         <v>19.7856</v>
+      </c>
+      <c r="V36">
+        <v>0.9307160188</v>
       </c>
       <c r="Z36">
         <v>9.9489</v>
@@ -2432,6 +2642,9 @@
       <c r="H37">
         <v>57.7</v>
       </c>
+      <c r="J37">
+        <v>9.08</v>
+      </c>
       <c r="N37">
         <v>55.2755</v>
       </c>
@@ -2455,6 +2668,9 @@
       </c>
       <c r="U37">
         <v>2.6707</v>
+      </c>
+      <c r="V37">
+        <v>0.0009335312254</v>
       </c>
       <c r="Z37">
         <v>6.9537</v>
@@ -2479,6 +2695,9 @@
       <c r="H38">
         <v>46.9</v>
       </c>
+      <c r="J38">
+        <v>9.32</v>
+      </c>
       <c r="N38">
         <v>85.72199999999999</v>
       </c>
@@ -2502,6 +2721,9 @@
       </c>
       <c r="U38">
         <v>2.1833</v>
+      </c>
+      <c r="V38">
+        <v>0.05275036151</v>
       </c>
       <c r="Z38">
         <v>7.6095</v>
@@ -2526,6 +2748,9 @@
       <c r="H39">
         <v>45.7</v>
       </c>
+      <c r="J39">
+        <v>8.949999999999999</v>
+      </c>
       <c r="N39">
         <v>105.9659</v>
       </c>
@@ -2549,6 +2774,9 @@
       </c>
       <c r="U39">
         <v>1.8883</v>
+      </c>
+      <c r="V39">
+        <v>0.03836049707</v>
       </c>
       <c r="Z39">
         <v>2.4245</v>
@@ -2573,6 +2801,9 @@
       <c r="H40">
         <v>59.6</v>
       </c>
+      <c r="J40">
+        <v>8.24</v>
+      </c>
       <c r="N40">
         <v>107.7763</v>
       </c>
@@ -2596,6 +2827,9 @@
       </c>
       <c r="U40">
         <v>4.2757</v>
+      </c>
+      <c r="V40">
+        <v>0.09394969043</v>
       </c>
       <c r="Z40">
         <v>13.1831</v>
@@ -2620,6 +2854,9 @@
       <c r="H41">
         <v>72</v>
       </c>
+      <c r="J41">
+        <v>9.369999999999999</v>
+      </c>
       <c r="N41">
         <v>136.4428</v>
       </c>
@@ -2643,6 +2880,9 @@
       </c>
       <c r="U41">
         <v>1.5886</v>
+      </c>
+      <c r="V41">
+        <v>0.001255321464</v>
       </c>
       <c r="Z41">
         <v>24.2219</v>
@@ -2667,6 +2907,9 @@
       <c r="H42">
         <v>58.8</v>
       </c>
+      <c r="J42">
+        <v>9.24</v>
+      </c>
       <c r="N42">
         <v>96.7711</v>
       </c>
@@ -2690,6 +2933,9 @@
       </c>
       <c r="U42">
         <v>1.6493</v>
+      </c>
+      <c r="V42">
+        <v>0.001185615282</v>
       </c>
       <c r="Z42">
         <v>11.3885</v>
@@ -2714,6 +2960,9 @@
       <c r="H43">
         <v>58.5</v>
       </c>
+      <c r="J43">
+        <v>9.15</v>
+      </c>
       <c r="N43">
         <v>94.90179999999999</v>
       </c>
@@ -2737,6 +2986,9 @@
       </c>
       <c r="U43">
         <v>1.5985</v>
+      </c>
+      <c r="V43">
+        <v>0.001176682409</v>
       </c>
       <c r="Z43">
         <v>11.3566</v>
